--- a/tests/M3-puja.xlsx
+++ b/tests/M3-puja.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -1186,6 +1186,231 @@
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
     </row>
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katha card only on the katha step</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katha card only on the katha step</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify no other step and no other puja shows a story</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the Vinayaka Chavithi puja.
+2. Look at each step.
+3. Open another puja if one is in this build.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the Vinayaka katha step shows Chavithi katha, 2 parts. Every other step is unchanged.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Part 1 then part 2</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Part 1 then part 2</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the katha plays the moon story and then the Syamantaka jewel</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On the katha step, tap the Chavithi katha card.
+2. Read to the end of part 1.
+3. Tap Continue.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Part 1 title is Chavithi katha, 1 of 2. The end of part 1 says Part 2: The Syamantaka jewel, with Continue. Part 2 title is Chavithi katha, 2 of 2.</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auto-continue follows Read to me</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auto-continue follows Read to me</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify part 2 starts by itself only when Read to me is on</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. With Read to me on, reach the end of part 1.
+2. Watch the countdown and tap Stay.
+3. Turn Read to me off and reach the end of part 1 again.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">With Read to me on, Continue in 3 is shown and part 2 starts after 3 seconds unless Stay is tapped. With Read to me off, the screen waits for Continue. Read to me stays hidden until narration files exist, so the waiting path is the one available today.</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back returns to the same guided step</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back returns to the same guided step</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify Back from the katha keeps the guided puja where it was</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the puja in guided mode and go to the katha step.
+2. Open the katha.
+3. Press Back.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The same katha step is showing, still in guided mode, with the ticks and the progress kept.</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resume the katha within 12 hours</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resume the katha within 12 hours</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify leaving mid-katha is remembered for 12 hours</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the katha and leave during part 1 or part 2.
+2. Return to the katha card within 12 hours.
+3. Finish part 2 and tap Back to the puja.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The card reads Continue, part 1 of 2, or part 2 of 2. After Back to the puja at the end of part 2, the card returns to Read or listen.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/M3-puja.xlsx
+++ b/tests/M3-puja.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -454,6 +454,7 @@
     <col width="24.140625" customWidth="1" min="7" max="7"/>
     <col width="26.5703125" customWidth="1" min="8" max="8"/>
     <col width="30.42578125" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +513,11 @@
           <t>Test Type</t>
         </is>
       </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Result</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="57.95" customHeight="1">
       <c r="A2" s="3" t="n">
@@ -1051,6 +1057,11 @@
       </c>
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not reached. The offering page was not opened while airplane mode was on.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="57.95" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -1185,6 +1196,11 @@
       </c>
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. With airplane mode on, Stories and the moon story opened and the music played. The puja text is on the phone.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="72" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -1230,6 +1246,11 @@
       </c>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. The card is on the katha step, guided step 24 of 32. The content check allows stories on that step only.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="72" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -1275,6 +1296,11 @@
       </c>
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Part 1 is the moon story and part 2 is the Syamantaka jewel. Part 1 ends on Continue. From the puja, part 2 ends on Back to the puja.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="72" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -1320,6 +1346,11 @@
       </c>
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS for the wait: Read to me is off, so part 1 stays until Continue. The three-second auto-continue is waiting for audio.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="72" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -1365,6 +1396,11 @@
       </c>
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Back from part 2 returns to guided step 24 of 32 with the same card and does not ask Continue from step 24. A fresh guided entry still asks that.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="72" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -1410,6 +1446,60 @@
       </c>
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. The card reads Continue · part 2 of 2. Finishing part 2 and Back to the puja had already returned it to Read or listen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katha card on the Vinayaka Chavithi observance page</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katha card on the Vinayaka Chavithi observance page</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the Chavithi katha card on the observance page</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Set the debug date to 14 Sep 2026.
+2. Open the calendar, day 14, then Vinayaka Chavithi.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under the families-do lines, the page shows the two-part Chavithi katha card.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Under What families do: Chavithi katha · 2 parts, The moon · The Syamantaka jewel, Continue · part 2 of 2. The accessibility name is Chavithi katha, 2 parts.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/M3-puja.xlsx
+++ b/tests/M3-puja.xlsx
@@ -652,6 +652,11 @@
       </c>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Pre, During and Post jump to those parts of the puja.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="57.95" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -697,6 +702,11 @@
       </c>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Durva shows No Durva grass? Akshata (rice with turmeric) is fine. The other items show the same kind of line.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="57.95" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -743,6 +753,11 @@
       </c>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. A durva tick was still there after the app was force-stopped. Clear ticks removed it.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="57.95" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -833,6 +848,11 @@
       </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. The patra step reached 21 of 21. Leaving the puja and opening it again showed 0 of 21. Practice totals stayed 112, 7 and 5.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="57.95" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -878,6 +898,11 @@
       </c>
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Guided mode shows one step at a time, with Previous and Next, and the screen stays on. Seen at step 24 of 32.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="57.95" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -923,6 +948,11 @@
       </c>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Opening guided mode again asked Continue from step 24.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="57.95" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -968,6 +998,11 @@
       </c>
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Telangana leads with Undrallu. Maharashtra leads with Modak. All five forms are on the page. The city was set back to Hyderabad.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="57.95" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1012,6 +1047,11 @@
       </c>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. The page has Why this offering, Offered on (Sankashti, Vinayaka Chavithi, and the puja), and the elder line.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="57.95" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1059,7 +1099,7 @@
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not reached. The offering page was not opened while airplane mode was on.</t>
+          <t xml:space="preserve">PASS. Search is on the page while the phone is online. With airplane mode and no network, the page still opens and Search is hidden.</t>
         </is>
       </c>
     </row>
@@ -1107,6 +1147,11 @@
       </c>
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. The 21 taps were not written. The japam totals were the same afterwards.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="57.95" customHeight="1">
       <c r="A15" s="3" t="n">

--- a/tests/M3-puja.xlsx
+++ b/tests/M3-puja.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -1546,6 +1546,642 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two-part step</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two-part step</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A guided step plays the instruction, then the mantra</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Vinayaka Chavithi guided mode.
+2. On a step that has both recordings, tap Play.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The instruction plays in the app language, then the mantra plays in Sanskrit. Nothing starts until Play is tapped.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Word lighting</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Word lighting</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The mantra word that is being read is lit</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Play a mantra step.
+2. Watch the mantra line.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each word is lit as it is read, in the script on screen.</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Script switch mid-step</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Script switch mid-step</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The script can change while the mantra is playing</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Play a mantra step.
+2. While it plays, switch Telugu script, संस्कृतम्, and IAST.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The line changes script and the lit word stays in place. The audio does not restart.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">List pause and the count</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">List pause and the count</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 21 names pause so each offering can be made</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Play the patri step once its list recording is in the pack.
+2. Listen through the names.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One name is lit at a time. The count reads like 7 of 21. Playback pauses about 3 seconds after each name.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hands-free countdown</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hands-free countdown</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hands-free moves on, and can be stopped</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On the guided start screen, leave Hands-free on.
+2. Play a step and let it finish.
+3. While the ring is on Next, try Pause, Back, and a tap on the ring.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Next shows a 4-second ring, then the next step. Pause freezes it and Play continues it. Back leaves the step and stops the ring. A tap on the ring stops it and stays on the step.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katha hands-free round trip</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katha hands-free round trip</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hands-free plays the Chavithi katha and returns</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. With Hands-free on, play the katha step once both story narrations are in the pack.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The moon story plays, then the Syamantaka story, then the puja returns and continues.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step with no audio waits</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step with no audio waits</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A step without a recording does not move by itself</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open guided mode before any puja recording is attached.
+2. Leave Hands-free on and look at Next.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The step keeps Previous and Next, as it does today. Hands-free does not move on until the person taps Next.</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not re-walked. The step keeps Previous and Next, and hands-free waits for Next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lock screen</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lock screen</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Playback continues on the lock screen</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Play a guided step.
+2. Lock the phone.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The notification reads Step N of 32 · the step title, with Play/Pause and Next. Audio keeps playing.</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language switch</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language switch</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changing language restarts only the instruction</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Play a step's instruction and switch the app language.
+2. Switch language again while the mantra is playing.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The instruction starts again in the new language. The mantra, once started, keeps playing.</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telugu, Hindi, and English</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telugu, Hindi, and English</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The instruction follows the app language</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Play one step in Telugu, Hindi, and English.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each language plays its own instruction. The mantra stays in Sanskrit.</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200% font</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200% font</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The guided controls still fit</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Set the font scale to 200%.
+2. Open guided mode.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hands-free, Back, Play, Next, the speed chips, and Repeat step stay tappable. Nothing is clipped to one letter a line.</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TalkBack</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TalkBack</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Play is named for the step</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Turn TalkBack on.
+2. Focus the play control on step 5.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TalkBack reads Play step 5.</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airplane mode</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airplane mode</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guided audio does not need the network</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Turn airplane mode on.
+2. Play a step whose recording is already on the phone.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The step plays. A step with no recording still waits for Next.</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for audio</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
